--- a/data/trans_orig/P57B3_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P57B3_R-Edad-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>9376</t>
+          <t>11317</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3216</t>
+          <t>4521</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23815</t>
+          <t>25518</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>23572</t>
+          <t>28493</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13070</t>
+          <t>17133</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>39744</t>
+          <t>47173</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>32948</t>
+          <t>39810</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>19265</t>
+          <t>25003</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>51721</t>
+          <t>60515</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,86%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>390611</t>
+          <t>396476</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>376172</t>
+          <t>382275</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>396771</t>
+          <t>403272</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>93,74%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>289628</t>
+          <t>334019</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>273456</t>
+          <t>315339</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>300130</t>
+          <t>345379</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>92,47%</t>
+          <t>92,14%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,31%</t>
+          <t>86,99%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>680239</t>
+          <t>730495</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>661466</t>
+          <t>709790</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>693922</t>
+          <t>745302</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>94,83%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>92,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>96,75%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>28230</t>
+          <t>36690</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18707</t>
+          <t>24662</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>44737</t>
+          <t>52593</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>37779</t>
+          <t>47283</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>23585</t>
+          <t>35960</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>52248</t>
+          <t>64915</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>66009</t>
+          <t>83973</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>48561</t>
+          <t>66265</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>86426</t>
+          <t>105417</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>10,78%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>395317</t>
+          <t>440200</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>378810</t>
+          <t>424297</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>404840</t>
+          <t>452228</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>92,31%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,44%</t>
+          <t>88,97%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>94,83%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>473725</t>
+          <t>453800</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>459256</t>
+          <t>436168</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>487919</t>
+          <t>465123</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>90,56%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,79%</t>
+          <t>87,05%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>92,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>869042</t>
+          <t>894000</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>848625</t>
+          <t>872556</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>886490</t>
+          <t>911708</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>91,41%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>89,22%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
+          <t>93,22%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>58822</t>
+          <t>74265</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>44059</t>
+          <t>59339</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>74522</t>
+          <t>93092</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>38913</t>
+          <t>47683</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>29927</t>
+          <t>36998</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>48683</t>
+          <t>61115</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>97735</t>
+          <t>121948</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>81461</t>
+          <t>103199</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>115886</t>
+          <t>146574</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>11,82%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>476491</t>
+          <t>545417</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>460791</t>
+          <t>526590</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>491254</t>
+          <t>560343</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>89,01%</t>
+          <t>88,02%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>86,08%</t>
+          <t>84,98%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,77%</t>
+          <t>90,42%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>501882</t>
+          <t>572691</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>492112</t>
+          <t>559259</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>510868</t>
+          <t>583376</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>92,31%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,0%</t>
+          <t>90,15%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>978373</t>
+          <t>1118108</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>960222</t>
+          <t>1093482</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>994647</t>
+          <t>1136857</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>90,92%</t>
+          <t>90,17%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,23%</t>
+          <t>88,18%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>91,68%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>535313</t>
+          <t>619682</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>535313</t>
+          <t>619682</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>535313</t>
+          <t>619682</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>540795</t>
+          <t>620374</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>540795</t>
+          <t>620374</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>540795</t>
+          <t>620374</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1076108</t>
+          <t>1240056</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1076108</t>
+          <t>1240056</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1076108</t>
+          <t>1240056</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>320013</t>
+          <t>83977</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>95773</t>
+          <t>68412</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>651082</t>
+          <t>103382</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>36,05%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>73,34%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>61051</t>
+          <t>72769</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>48509</t>
+          <t>59176</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>74475</t>
+          <t>86179</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>381065</t>
+          <t>156746</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>151201</t>
+          <t>135039</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>917479</t>
+          <t>178311</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>57,36%</t>
+          <t>12,41%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>567773</t>
+          <t>616640</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>236704</t>
+          <t>597235</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>792013</t>
+          <t>632205</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>63,95%</t>
+          <t>88,01%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>85,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,21%</t>
+          <t>90,24%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>650764</t>
+          <t>663022</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>637340</t>
+          <t>649612</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>663306</t>
+          <t>676615</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>91,42%</t>
+          <t>90,11%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,54%</t>
+          <t>88,29%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>91,96%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1218537</t>
+          <t>1279662</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>682123</t>
+          <t>1258097</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1448401</t>
+          <t>1301369</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>76,18%</t>
+          <t>89,09%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>42,64%</t>
+          <t>87,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>90,6%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>711815</t>
+          <t>735791</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>711815</t>
+          <t>735791</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>711815</t>
+          <t>735791</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1599602</t>
+          <t>1436408</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1599602</t>
+          <t>1436408</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1599602</t>
+          <t>1436408</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>93402</t>
+          <t>103311</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>78362</t>
+          <t>85992</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>110483</t>
+          <t>121118</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>81163</t>
+          <t>91395</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>69767</t>
+          <t>77797</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>93343</t>
+          <t>105837</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>174566</t>
+          <t>194706</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>155349</t>
+          <t>174266</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>195747</t>
+          <t>217913</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,91%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>467832</t>
+          <t>506035</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>450751</t>
+          <t>488228</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>482872</t>
+          <t>523354</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>83,36%</t>
+          <t>83,05%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>80,31%</t>
+          <t>80,12%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>86,04%</t>
+          <t>85,89%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>465531</t>
+          <t>516119</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>453351</t>
+          <t>501677</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>476927</t>
+          <t>529717</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>85,15%</t>
+          <t>84,96%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>82,93%</t>
+          <t>82,58%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>87,24%</t>
+          <t>87,19%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>933362</t>
+          <t>1022154</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>912181</t>
+          <t>998947</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>952579</t>
+          <t>1042594</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>84,24%</t>
+          <t>84,0%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>82,33%</t>
+          <t>82,09%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>85,98%</t>
+          <t>85,68%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>546694</t>
+          <t>607514</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>546694</t>
+          <t>607514</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>546694</t>
+          <t>607514</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1107928</t>
+          <t>1216860</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1107928</t>
+          <t>1216860</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1107928</t>
+          <t>1216860</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2440,32 +2440,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>46267</t>
+          <t>50117</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>36890</t>
+          <t>39025</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>56824</t>
+          <t>61212</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,32 +2475,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>79196</t>
+          <t>87670</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>35793</t>
+          <t>75419</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>125401</t>
+          <t>98930</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>19,96%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>125463</t>
+          <t>137787</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>66290</t>
+          <t>122448</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>165595</t>
+          <t>153947</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>18,19%</t>
         </is>
       </c>
     </row>
@@ -2553,32 +2553,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>321898</t>
+          <t>356963</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>311341</t>
+          <t>345868</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>331275</t>
+          <t>368055</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>87,43%</t>
+          <t>87,69%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>84,57%</t>
+          <t>84,96%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>89,98%</t>
+          <t>90,41%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,32 +2588,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>529172</t>
+          <t>351496</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>482967</t>
+          <t>340236</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>572575</t>
+          <t>363747</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>86,98%</t>
+          <t>80,04%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>79,39%</t>
+          <t>77,47%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>82,83%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>851070</t>
+          <t>708459</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>810938</t>
+          <t>692299</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>910243</t>
+          <t>723798</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>87,15%</t>
+          <t>83,72%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>83,04%</t>
+          <t>81,81%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>85,53%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,32 +2783,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>53223</t>
+          <t>57362</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>44082</t>
+          <t>46864</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>62780</t>
+          <t>68286</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>22,08%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,32 +2818,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>118815</t>
+          <t>129515</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>106304</t>
+          <t>116695</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>131610</t>
+          <t>144847</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>28,0%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>25,22%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>31,04%</t>
+          <t>31,31%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>172038</t>
+          <t>186877</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>156265</t>
+          <t>170143</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>189921</t>
+          <t>206191</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>24,21%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>26,91%</t>
+          <t>26,71%</t>
         </is>
       </c>
     </row>
@@ -2896,32 +2896,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>228669</t>
+          <t>251909</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>219112</t>
+          <t>240985</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>237810</t>
+          <t>262407</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>81,12%</t>
+          <t>81,45%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>77,73%</t>
+          <t>77,92%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>84,36%</t>
+          <t>84,85%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,32 +2931,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>305141</t>
+          <t>333106</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>292346</t>
+          <t>317774</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>317652</t>
+          <t>345926</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>71,97%</t>
+          <t>72,0%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>68,96%</t>
+          <t>68,69%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>74,93%</t>
+          <t>74,78%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>533809</t>
+          <t>585015</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>515926</t>
+          <t>565701</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>549582</t>
+          <t>601749</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>75,63%</t>
+          <t>75,79%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>73,09%</t>
+          <t>73,29%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>77,86%</t>
+          <t>77,96%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>281892</t>
+          <t>309271</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>281892</t>
+          <t>309271</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>281892</t>
+          <t>309271</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>423956</t>
+          <t>462621</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>423956</t>
+          <t>462621</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>423956</t>
+          <t>462621</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>705847</t>
+          <t>771892</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>705847</t>
+          <t>771892</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>705847</t>
+          <t>771892</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3126,32 +3126,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>609334</t>
+          <t>417039</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>379463</t>
+          <t>378278</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1280857</t>
+          <t>460031</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>37,04%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,32 +3161,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>440490</t>
+          <t>504807</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>358236</t>
+          <t>470570</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>482937</t>
+          <t>542857</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,32 +3196,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>1049824</t>
+          <t>921846</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>820712</t>
+          <t>872490</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1872786</t>
+          <t>975451</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>13,44%</t>
         </is>
       </c>
     </row>
@@ -3239,32 +3239,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>2848590</t>
+          <t>3113641</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2177067</t>
+          <t>3070649</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3078461</t>
+          <t>3152402</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>82,38%</t>
+          <t>88,19%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>62,96%</t>
+          <t>86,97%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>89,03%</t>
+          <t>89,29%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,32 +3274,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>3215843</t>
+          <t>3224253</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3173396</t>
+          <t>3186203</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3298097</t>
+          <t>3258490</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>87,95%</t>
+          <t>86,46%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>86,79%</t>
+          <t>85,44%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>90,2%</t>
+          <t>87,38%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,32 +3309,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>6064433</t>
+          <t>6337894</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5241471</t>
+          <t>6284289</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6293545</t>
+          <t>6387250</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>85,24%</t>
+          <t>87,3%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>73,68%</t>
+          <t>86,56%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>88,46%</t>
+          <t>87,98%</t>
         </is>
       </c>
     </row>
@@ -3352,17 +3352,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3457924</t>
+          <t>3530680</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3457924</t>
+          <t>3530680</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3457924</t>
+          <t>3530680</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3387,17 +3387,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3656333</t>
+          <t>3729060</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3656333</t>
+          <t>3729060</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3656333</t>
+          <t>3729060</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7114257</t>
+          <t>7259740</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7114257</t>
+          <t>7259740</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7114257</t>
+          <t>7259740</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
